--- a/excel_filer/may_unmatched_filenames_full.xlsx
+++ b/excel_filer/may_unmatched_filenames_full.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,14 +619,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CS_Right Hallux_L1097_S3565__31_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S2018__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L1097</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -647,18 +647,18 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3565</v>
+        <v>2018</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" s="2" t="n">
-        <v>44347</v>
+        <v>44334</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2018__18_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S2019__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" s="2" t="n">
@@ -697,7 +697,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2019__18_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S2081__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2019</v>
+        <v>2081</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" s="2" t="n">
@@ -736,26 +736,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1833__17_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S2957__26_05_2021.dcm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -764,37 +764,37 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1833</v>
+        <v>2957</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>44333</v>
+        <v>44342</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1834__17_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S2958__26_05_2021.dcm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1834</v>
+        <v>2958</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>44333</v>
+        <v>44342</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1835__17_05_2021.dcm</t>
+          <t>GM_Right Hallux_L1041_S3009__26_05_2021.dcm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1041</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -842,25 +842,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1835</v>
+        <v>3009</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" s="2" t="n">
-        <v>44333</v>
+        <v>44342</v>
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1836__17_05_2021.dcm</t>
+          <t>HB_Right Hand_L1052_S2443__21_05_2021.dcm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1052</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -881,25 +881,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1836</v>
+        <v>2443</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>44333</v>
+        <v>44337</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1837__17_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3100__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -920,25 +920,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1837</v>
+        <v>3100</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>44333</v>
+        <v>44343</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DH_Right Hand_L1027_S1838__17_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3101__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L1027</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -959,37 +959,37 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1838</v>
+        <v>3101</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" s="2" t="n">
-        <v>44333</v>
+        <v>44343</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2081__18_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3102__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2081</v>
+        <v>3102</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>44334</v>
+        <v>44343</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2956__26_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3103__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1037,37 +1037,37 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2956</v>
+        <v>3103</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2957__26_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3104__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1076,37 +1076,37 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2957</v>
+        <v>3104</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="2" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2958__26_05_2021.dcm</t>
+          <t>HL_Right Hand_L1048_S3117__27_05_2021.dcm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1048</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1115,25 +1115,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2958</v>
+        <v>3117</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>44342</v>
+        <v>44343</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2959__26_05_2021.dcm</t>
+          <t>HR_Right Hallux_L1057_S2551__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1057</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1154,37 +1154,37 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2959</v>
+        <v>2551</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>44342</v>
+        <v>44340</v>
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2960__26_05_2021.dcm</t>
+          <t>HR_Right Hand_L1056_S2538__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1056</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1193,37 +1193,37 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2960</v>
+        <v>2538</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" s="2" t="n">
-        <v>44342</v>
+        <v>44340</v>
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S2961__26_05_2021.dcm</t>
+          <t>JF_Right Hand_L1011_S221__07_05_2021.dcm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1011</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1232,37 +1232,37 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2961</v>
+        <v>221</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>44342</v>
+        <v>44323</v>
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GM_Right Hallux_L1041_S3009__26_05_2021.dcm</t>
+          <t>JF_Right Hand_L1011_S223__07_05_2021.dcm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>L1041</t>
+          <t>L1011</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1271,37 +1271,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3009</v>
+        <v>223</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>44342</v>
+        <v>44323</v>
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HB_Right Hand_L1052_S2443__21_05_2021.dcm</t>
+          <t>JF_Right Instep_L1012_S206__07_05_2021.dcm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>L1052</t>
+          <t>L1012</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1310,37 +1310,37 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2443</v>
+        <v>206</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" s="2" t="n">
-        <v>44337</v>
+        <v>44323</v>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3100__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1760__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1349,37 +1349,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3100</v>
+        <v>1760</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3101__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1761__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1388,37 +1388,37 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3101</v>
+        <v>1761</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3102__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1762__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3102</v>
+        <v>1762</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3103__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1763__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1466,37 +1466,37 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3103</v>
+        <v>1763</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3104__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1764__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1505,37 +1505,37 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3104</v>
+        <v>1764</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HL_Right Hand_L1048_S3117__27_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S1765__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>L1048</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1544,25 +1544,25 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3117</v>
+        <v>1765</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="2" t="n">
-        <v>44343</v>
+        <v>44330</v>
       </c>
       <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HR_Right Hallux_L1057_S2551__24_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S2667__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>L1057</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2551</v>
+        <v>2667</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" s="2" t="n">
@@ -1594,26 +1594,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HR_Right Hand_L1056_S2538__24_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S2721__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>L1056</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2538</v>
+        <v>2721</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" s="2" t="n">
@@ -1633,26 +1633,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JF_Right Hand_L1011_S221__07_05_2021.dcm</t>
+          <t>JJ_Right Hallux_L1030_S2722__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>L1011</t>
+          <t>L1030</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1661,25 +1661,25 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>221</v>
+        <v>2722</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" s="2" t="n">
-        <v>44323</v>
+        <v>44340</v>
       </c>
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JF_Right Hand_L1011_S223__07_05_2021.dcm</t>
+          <t>JJ_Right Hand_L1029_S2654__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>L1011</t>
+          <t>L1029</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1700,25 +1700,25 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>223</v>
+        <v>2654</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>44323</v>
+        <v>44340</v>
       </c>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JF_Right Instep_L1012_S206__07_05_2021.dcm</t>
+          <t>JR_Right Hallux_L1018_S1627__14_05_2021.dcm</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>L1012</t>
+          <t>L1018</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1739,25 +1739,25 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>206</v>
+        <v>1627</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1760__14_05_2021.dcm</t>
+          <t>LM_Right Hallux_L1087_S3328__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1087</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1778,37 +1778,37 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1760</v>
+        <v>3328</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" s="2" t="n">
-        <v>44330</v>
+        <v>44344</v>
       </c>
       <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1761__14_05_2021.dcm</t>
+          <t>LB_Right Hand_L1083_S4189__04_06_2021.dcm</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1761</v>
+        <v>4189</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>44330</v>
+        <v>44351</v>
       </c>
       <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1762__14_05_2021.dcm</t>
+          <t>LT_Right Hand_L1098_S3766__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1856,37 +1856,37 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1762</v>
+        <v>3766</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>44330</v>
+        <v>44349</v>
       </c>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1763__14_05_2021.dcm</t>
+          <t>LT_Right Hand_L1098_S3627__01_06_2021.dcm</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1895,25 +1895,25 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1763</v>
+        <v>3627</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" s="2" t="n">
-        <v>44330</v>
+        <v>44348</v>
       </c>
       <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1764__14_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3994__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1934,25 +1934,25 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1764</v>
+        <v>3994</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>44330</v>
+        <v>44350</v>
       </c>
       <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S1765__14_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3995__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1973,25 +1973,25 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1765</v>
+        <v>3995</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>44330</v>
+        <v>44350</v>
       </c>
       <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S2667__24_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3996__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2012,25 +2012,25 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2667</v>
+        <v>3996</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" s="2" t="n">
-        <v>44340</v>
+        <v>44350</v>
       </c>
       <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S2721__24_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3997__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2721</v>
+        <v>3997</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>44340</v>
+        <v>44350</v>
       </c>
       <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JJ_Right Hallux_L1030_S2722__24_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3998__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L1030</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2090,37 +2090,37 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>2722</v>
+        <v>3998</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>44340</v>
+        <v>44350</v>
       </c>
       <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JJ_Right Hand_L1029_S2654__24_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S3999__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L1029</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2129,37 +2129,37 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>2654</v>
+        <v>3999</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" s="2" t="n">
-        <v>44340</v>
+        <v>44350</v>
       </c>
       <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JR_Right Hallux_L1018_S1627__14_05_2021.dcm</t>
+          <t>TA_Right Hand_L1021_S2112__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>L1018</t>
+          <t>L1021</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1627</v>
+        <v>2112</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>44330</v>
+        <v>44334</v>
       </c>
       <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LM_Right Hallux_L1087_S3328__28_05_2021.dcm</t>
+          <t>TA_Right Hand_L1021_S2126__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>L1087</t>
+          <t>L1021</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2207,37 +2207,37 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>3328</v>
+        <v>2126</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>44344</v>
+        <v>44334</v>
       </c>
       <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LB_Right Hand_L1083_S4189__04_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3278__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L1083</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>4189</v>
+        <v>3278</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" s="2" t="n">
-        <v>44351</v>
+        <v>44344</v>
       </c>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LT_Right Hand_L1098_S3766__02_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3279__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3766</v>
+        <v>3279</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>44349</v>
+        <v>44344</v>
       </c>
       <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LT_Right Hand_L1098_S3627__01_06_2021.dcm</t>
+          <t>LB_Right Hand_L1083_S3258__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1083</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2324,25 +2324,25 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>3627</v>
+        <v>3258</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>44348</v>
+        <v>44344</v>
       </c>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3994__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3280__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>3994</v>
+        <v>3280</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3995__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3281__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2402,25 +2402,25 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3995</v>
+        <v>3281</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3996__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3282__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2441,25 +2441,25 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3996</v>
+        <v>3282</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3997__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S3283__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2480,25 +2480,25 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>3997</v>
+        <v>3283</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3998__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S4198__04_06_2021.dcm</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>3998</v>
+        <v>4198</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>44350</v>
+        <v>44351</v>
       </c>
       <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S3999__03_06_2021.dcm</t>
+          <t>LB_Right Hallux_L1084_S4205__04_06_2021.dcm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1084</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2558,25 +2558,25 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>3999</v>
+        <v>4205</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>44350</v>
+        <v>44351</v>
       </c>
       <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TA_Right Hand_L1021_S2112__18_05_2021.dcm</t>
+          <t>LM_Right Hand_L1086_S3314__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L1021</t>
+          <t>L1086</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2597,37 +2597,37 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>2112</v>
+        <v>3314</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="2" t="n">
-        <v>44334</v>
+        <v>44344</v>
       </c>
       <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TA_Right Hand_L1021_S2126__18_05_2021.dcm</t>
+          <t>MB_Right Hallux_L1066_S2860__25_05_2021.dcm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L1021</t>
+          <t>L1066</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2636,37 +2636,37 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2126</v>
+        <v>2860</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>44334</v>
+        <v>44341</v>
       </c>
       <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3278__28_05_2021.dcm</t>
+          <t>MJ_Right Hand_L1100_S3688__01_06_2021.dcm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1100</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2675,37 +2675,37 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>3278</v>
+        <v>3688</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>44344</v>
+        <v>44348</v>
       </c>
       <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3279__28_05_2021.dcm</t>
+          <t>LT_Right Hand_L1098_S3818__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1098</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2714,37 +2714,37 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3279</v>
+        <v>3818</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="2" t="n">
-        <v>44344</v>
+        <v>44349</v>
       </c>
       <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LB_Right Hand_L1083_S3258__28_05_2021.dcm</t>
+          <t>MO_Right Hallux_L1104_S4094__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L1083</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2753,25 +2753,25 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>3258</v>
+        <v>4094</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="2" t="n">
-        <v>44344</v>
+        <v>44350</v>
       </c>
       <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3280__28_05_2021.dcm</t>
+          <t>MO_Right Hallux_L1104_S4095__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>3280</v>
+        <v>4095</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="2" t="n">
-        <v>44344</v>
+        <v>44350</v>
       </c>
       <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3281__28_05_2021.dcm</t>
+          <t>MO_Right Hallux_L1104_S4096__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2831,25 +2831,25 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3281</v>
+        <v>4096</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" s="2" t="n">
-        <v>44344</v>
+        <v>44350</v>
       </c>
       <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3282__28_05_2021.dcm</t>
+          <t>PW_Right Hallux_L1107_S4179__04_06_2021.dcm</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1107</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2870,37 +2870,37 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3282</v>
+        <v>4179</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>44344</v>
+        <v>44351</v>
       </c>
       <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S3283__28_05_2021.dcm</t>
+          <t>PW_Right Hand_L1106_S3987__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1106</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2909,25 +2909,25 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3283</v>
+        <v>3987</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>44344</v>
+        <v>44350</v>
       </c>
       <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S4198__04_06_2021.dcm</t>
+          <t>RH_Right Hallux_L1014_S1463__11_05_2021.dcm</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1014</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2948,25 +2948,25 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>4198</v>
+        <v>1463</v>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" s="2" t="n">
-        <v>44351</v>
+        <v>44327</v>
       </c>
       <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LB_Right Hallux_L1084_S4205__04_06_2021.dcm</t>
+          <t>RH_Right Hallux_L1014_S1520__11_05_2021.dcm</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L1084</t>
+          <t>L1014</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2987,37 +2987,37 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4205</v>
+        <v>1520</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>44351</v>
+        <v>44327</v>
       </c>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LM_Right Hand_L1086_S3314__28_05_2021.dcm</t>
+          <t>RS_Right Hallux_L1076_S3033__26_05_2021.dcm</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>L1086</t>
+          <t>L1076</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>3314</v>
+        <v>3033</v>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>44344</v>
+        <v>44342</v>
       </c>
       <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB_Right Hallux_L1066_S2860__25_05_2021.dcm</t>
+          <t>RS_Right Hand_L1074_S3893__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L1066</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3065,25 +3065,25 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>2860</v>
+        <v>3893</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="2" t="n">
-        <v>44341</v>
+        <v>44349</v>
       </c>
       <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MJ_Right Hand_L1100_S3688__01_06_2021.dcm</t>
+          <t>RS_Right Hand_L1074_S3894__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>L1100</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3104,25 +3104,25 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3688</v>
+        <v>3894</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="2" t="n">
-        <v>44348</v>
+        <v>44349</v>
       </c>
       <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LT_Right Hand_L1098_S3818__02_06_2021.dcm</t>
+          <t>RS_Right Hand_L1074_S3895__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>L1098</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3818</v>
+        <v>3895</v>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" s="2" t="n">
@@ -3154,26 +3154,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MO_Right Hallux_L1104_S4094__03_06_2021.dcm</t>
+          <t>RS_Right Hand_L1074_S3896__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1074</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3182,18 +3182,18 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>4094</v>
+        <v>3896</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" s="2" t="n">
-        <v>44350</v>
+        <v>44349</v>
       </c>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MO_Right Hallux_L1104_S4095__03_06_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S3925__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3206,13 +3206,13 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3221,18 +3221,18 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>4095</v>
+        <v>3925</v>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" s="2" t="n">
-        <v>44350</v>
+        <v>44349</v>
       </c>
       <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MO_Right Hallux_L1104_S4096__03_06_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4034__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3245,13 +3245,13 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>4096</v>
+        <v>4034</v>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" s="2" t="n">
@@ -3271,26 +3271,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PW_Right Hallux_L1107_S4179__04_06_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4035__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L1107</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3299,25 +3299,25 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>4179</v>
+        <v>4035</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" s="2" t="n">
-        <v>44351</v>
+        <v>44350</v>
       </c>
       <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PW_Right Hand_L1106_S3987__03_06_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4036__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>L1106</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>3987</v>
+        <v>4036</v>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" s="2" t="n">
@@ -3349,26 +3349,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RH_Right Hallux_L1014_S1463__11_05_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4037__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>L1014</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3377,37 +3377,37 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1463</v>
+        <v>4037</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" s="2" t="n">
-        <v>44327</v>
+        <v>44350</v>
       </c>
       <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RH_Right Hallux_L1014_S1520__11_05_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4038__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>L1014</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3416,37 +3416,37 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1520</v>
+        <v>4038</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" s="2" t="n">
-        <v>44327</v>
+        <v>44350</v>
       </c>
       <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RS_Right Hallux_L1076_S3033__26_05_2021.dcm</t>
+          <t>MO_Right Hand_L1104_S4039__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>L1076</t>
+          <t>L1104</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3455,25 +3455,25 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>3033</v>
+        <v>4039</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" s="2" t="n">
-        <v>44342</v>
+        <v>44350</v>
       </c>
       <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RS_Right Hand_L1074_S3893__02_06_2021.dcm</t>
+          <t>NL_Right Hand_L1108_S4000__03_06_2021.dcm</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>L1074</t>
+          <t>L1108</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3494,25 +3494,25 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>3893</v>
+        <v>4000</v>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" s="2" t="n">
-        <v>44349</v>
+        <v>44350</v>
       </c>
       <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RS_Right Hand_L1074_S3894__02_06_2021.dcm</t>
+          <t>NB_Right Hand_L1043_S2196__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>L1074</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3533,25 +3533,25 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>3894</v>
+        <v>2196</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" s="2" t="n">
-        <v>44349</v>
+        <v>44335</v>
       </c>
       <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RS_Right Hand_L1074_S3895__02_06_2021.dcm</t>
+          <t>NB_Right Hand_L1043_S2197__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>L1074</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3572,25 +3572,25 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>3895</v>
+        <v>2197</v>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" s="2" t="n">
-        <v>44349</v>
+        <v>44335</v>
       </c>
       <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RS_Right Hand_L1074_S3896__02_06_2021.dcm</t>
+          <t>NB_Right Hand_L1043_S2198__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>L1074</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3611,25 +3611,25 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3896</v>
+        <v>2198</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" s="2" t="n">
-        <v>44349</v>
+        <v>44335</v>
       </c>
       <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S3925__02_06_2021.dcm</t>
+          <t>NB_Right Hand_L1043_S2199__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1043</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3650,37 +3650,37 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>3925</v>
+        <v>2199</v>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" s="2" t="n">
-        <v>44349</v>
+        <v>44335</v>
       </c>
       <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4034__03_06_2021.dcm</t>
+          <t>TJ_Right Hallux_L1093_S3428__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3689,37 +3689,37 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>4034</v>
+        <v>3428</v>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4035__03_06_2021.dcm</t>
+          <t>TJ_Right Hallux_L1093_S3429__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3728,37 +3728,37 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>4035</v>
+        <v>3429</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4036__03_06_2021.dcm</t>
+          <t>TJ_Right Hallux_L1093_S3430__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3767,37 +3767,37 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>4036</v>
+        <v>3430</v>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4037__03_06_2021.dcm</t>
+          <t>TJ_Right Hallux_L1093_S3431__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3806,37 +3806,37 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>4037</v>
+        <v>3431</v>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4038__03_06_2021.dcm</t>
+          <t>TJ_Right Hallux_L1093_S3432__28_05_2021.dcm</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1093</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3845,37 +3845,37 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>4038</v>
+        <v>3432</v>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" s="2" t="n">
-        <v>44350</v>
+        <v>44344</v>
       </c>
       <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MO_Right Hand_L1104_S4039__03_06_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S520__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>L1104</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3884,37 +3884,37 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>4039</v>
+        <v>520</v>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" s="2" t="n">
-        <v>44350</v>
+        <v>44117</v>
       </c>
       <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NL_Right Hand_L1108_S4000__03_06_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S521__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>L1108</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4000</v>
+        <v>521</v>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" s="2" t="n">
-        <v>44350</v>
+        <v>44117</v>
       </c>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NB_Right Hand_L1043_S2196__19_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S522__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -3962,37 +3962,37 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>2196</v>
+        <v>522</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" s="2" t="n">
-        <v>44335</v>
+        <v>44117</v>
       </c>
       <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NB_Right Hand_L1043_S2197__19_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S523__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4001,37 +4001,37 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2197</v>
+        <v>523</v>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" s="2" t="n">
-        <v>44335</v>
+        <v>44117</v>
       </c>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NB_Right Hand_L1043_S2198__19_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S524__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4040,37 +4040,37 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>2198</v>
+        <v>524</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" s="2" t="n">
-        <v>44335</v>
+        <v>44117</v>
       </c>
       <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NB_Right Hand_L1043_S2199__19_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S525__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>L1043</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4079,25 +4079,25 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>2199</v>
+        <v>525</v>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" s="2" t="n">
-        <v>44335</v>
+        <v>44117</v>
       </c>
       <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TJ_Right Hallux_L1093_S3428__28_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S526__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4109,7 +4109,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4118,25 +4118,25 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>3428</v>
+        <v>526</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" s="2" t="n">
-        <v>44344</v>
+        <v>44117</v>
       </c>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TJ_Right Hallux_L1093_S3429__28_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S527__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4148,7 +4148,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4157,25 +4157,25 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>3429</v>
+        <v>527</v>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" s="2" t="n">
-        <v>44344</v>
+        <v>44117</v>
       </c>
       <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TJ_Right Hallux_L1093_S3430__28_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S528__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4196,25 +4196,25 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>3430</v>
+        <v>528</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" s="2" t="n">
-        <v>44344</v>
+        <v>44117</v>
       </c>
       <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TJ_Right Hallux_L1093_S3431__28_05_2021.dcm</t>
+          <t>TL_Right Instep_L1038_S529__13_10_2020.dcm</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1038</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Instep</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4235,37 +4235,37 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>3431</v>
+        <v>529</v>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" s="2" t="n">
-        <v>44344</v>
+        <v>44117</v>
       </c>
       <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TJ_Right Hallux_L1093_S3432__28_05_2021.dcm</t>
+          <t>VF_Right Hand_L1023_S1568__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>L1093</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4274,37 +4274,37 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>3432</v>
+        <v>1568</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" s="2" t="n">
-        <v>44344</v>
+        <v>44328</v>
       </c>
       <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S520__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1569__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4313,37 +4313,37 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>520</v>
+        <v>1569</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S521__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1570__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4352,37 +4352,37 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>521</v>
+        <v>1570</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S522__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1571__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4391,37 +4391,37 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>522</v>
+        <v>1571</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S523__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1572__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4430,37 +4430,37 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>523</v>
+        <v>1572</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S524__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1573__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4469,37 +4469,37 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>524</v>
+        <v>1573</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S525__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1574__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4508,37 +4508,37 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>525</v>
+        <v>1574</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S526__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1575__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4547,37 +4547,37 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>526</v>
+        <v>1575</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S527__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1576__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4586,37 +4586,37 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>527</v>
+        <v>1576</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S528__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1577__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4625,37 +4625,37 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>528</v>
+        <v>1577</v>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TL_Right Instep_L1038_S529__13_10_2020.dcm</t>
+          <t>VF_Right Hand_L1023_S1578__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>L1038</t>
+          <t>L1023</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Instep</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4664,18 +4664,18 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>529</v>
+        <v>1578</v>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" s="2" t="n">
-        <v>44117</v>
+        <v>44328</v>
       </c>
       <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1568__12_05_2021.dcm</t>
+          <t>VF_Right Hand_L1023_S1579__12_05_2021.dcm</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1568</v>
+        <v>1579</v>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" s="2" t="n">
@@ -4714,26 +4714,26 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1569__12_05_2021.dcm</t>
+          <t>WL_Right Hallux_L1073_S2981__26_05_2021.dcm</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1073</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4742,25 +4742,25 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1569</v>
+        <v>2981</v>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" s="2" t="n">
-        <v>44328</v>
+        <v>44342</v>
       </c>
       <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1570__12_05_2021.dcm</t>
+          <t>AC_Right Hand_L1050_S2374__20_05_2021.dcm</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1050</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4781,25 +4781,25 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>1570</v>
+        <v>2374</v>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" s="2" t="n">
-        <v>44328</v>
+        <v>44336</v>
       </c>
       <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1571__12_05_2021.dcm</t>
+          <t>AC_Right Hand_L1050_S2580__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1050</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4820,25 +4820,25 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1571</v>
+        <v>2580</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" s="2" t="n">
-        <v>44328</v>
+        <v>44340</v>
       </c>
       <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1572__12_05_2021.dcm</t>
+          <t>AC_Right Hand_L1050_S2581__24_05_2021.dcm</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1050</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4859,25 +4859,25 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>1572</v>
+        <v>2581</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" s="2" t="n">
-        <v>44328</v>
+        <v>44340</v>
       </c>
       <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1573__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S152__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4898,25 +4898,25 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>1573</v>
+        <v>152</v>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1574__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S153__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4937,25 +4937,25 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>1574</v>
+        <v>153</v>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1575__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S154__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4976,25 +4976,25 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1575</v>
+        <v>154</v>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1576__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S155__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -5015,25 +5015,25 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>1576</v>
+        <v>155</v>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1577__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S156__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5054,25 +5054,25 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1577</v>
+        <v>156</v>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1578__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S159__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -5093,25 +5093,25 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>1578</v>
+        <v>159</v>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VF_Right Hand_L1023_S1579__12_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S160__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>L1023</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -5132,37 +5132,37 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>1579</v>
+        <v>160</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" s="2" t="n">
-        <v>44328</v>
+        <v>44322</v>
       </c>
       <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WL_Right Hallux_L1073_S2981__26_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S161__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>L1073</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5171,25 +5171,25 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>2981</v>
+        <v>161</v>
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" s="2" t="n">
-        <v>44342</v>
+        <v>44322</v>
       </c>
       <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AC_Right Hand_L1050_S2374__20_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S162__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>L1050</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5210,25 +5210,25 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>2374</v>
+        <v>162</v>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" s="2" t="n">
-        <v>44336</v>
+        <v>44322</v>
       </c>
       <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AC_Right Hand_L1050_S2580__24_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S163__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>L1050</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -5249,25 +5249,25 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>2580</v>
+        <v>163</v>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" s="2" t="n">
-        <v>44340</v>
+        <v>44322</v>
       </c>
       <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AC_Right Hand_L1050_S2581__24_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S164__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>L1050</t>
+          <t>L1008</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -5288,18 +5288,18 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>2581</v>
+        <v>164</v>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" s="2" t="n">
-        <v>44340</v>
+        <v>44322</v>
       </c>
       <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S152__06_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S165__06_05_2021.dcm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" s="2" t="n">
@@ -5338,7 +5338,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S153__06_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S2158__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>153</v>
+        <v>2158</v>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S154__06_05_2021.dcm</t>
+          <t>AKD_Right Hand_L1008_S2159__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5405,25 +5405,25 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>154</v>
+        <v>2159</v>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S155__06_05_2021.dcm</t>
+          <t>AT_Right Hand_L1094_S3743__02_06_2021.dcm</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1094</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5444,25 +5444,25 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>155</v>
+        <v>3743</v>
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" s="2" t="n">
-        <v>44322</v>
+        <v>44349</v>
       </c>
       <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S156__06_05_2021.dcm</t>
+          <t>BB_Right Middle Finger_L1047_S2245__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5474,7 +5474,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Middle Finger</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5483,25 +5483,25 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>156</v>
+        <v>2245</v>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S159__06_05_2021.dcm</t>
+          <t>BB_Right Middle Finger_L1047_S2247__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Middle Finger</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5522,25 +5522,25 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>159</v>
+        <v>2247</v>
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S160__06_05_2021.dcm</t>
+          <t>BB_Right Middle Finger_L1047_S2248__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5552,7 +5552,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Middle Finger</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>160</v>
+        <v>2248</v>
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S161__06_05_2021.dcm</t>
+          <t>BB_Right Middle Finger_L1047_S2249__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5591,7 +5591,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Middle Finger</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5600,25 +5600,25 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>161</v>
+        <v>2249</v>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S162__06_05_2021.dcm</t>
+          <t>BB_Right Middle Finger_L1047_S2250__19_05_2021.dcm</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1047</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5630,7 +5630,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Middle Finger</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5639,37 +5639,37 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>162</v>
+        <v>2250</v>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" s="2" t="n">
-        <v>44322</v>
+        <v>44335</v>
       </c>
       <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S163__06_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3482__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5678,37 +5678,37 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>163</v>
+        <v>3482</v>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" s="2" t="n">
-        <v>44322</v>
+        <v>44347</v>
       </c>
       <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S164__06_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3534__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5717,37 +5717,37 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>164</v>
+        <v>3534</v>
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" s="2" t="n">
-        <v>44322</v>
+        <v>44347</v>
       </c>
       <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S165__06_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3535__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5756,37 +5756,37 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>165</v>
+        <v>3535</v>
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" s="2" t="n">
-        <v>44322</v>
+        <v>44347</v>
       </c>
       <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S2158__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3536__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5795,37 +5795,37 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>2158</v>
+        <v>3536</v>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AKD_Right Hand_L1008_S2159__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3537__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>L1008</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -5834,37 +5834,37 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>2159</v>
+        <v>3537</v>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AT_Right Hand_L1094_S3743__02_06_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3538__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>L1094</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -5873,37 +5873,37 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>3743</v>
+        <v>3538</v>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" s="2" t="n">
-        <v>44349</v>
+        <v>44347</v>
       </c>
       <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BB_Right Middle Finger_L1047_S2245__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3539__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Middle Finger</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -5912,37 +5912,37 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>2245</v>
+        <v>3539</v>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BB_Right Middle Finger_L1047_S2247__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3540__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Middle Finger</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -5951,37 +5951,37 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>2247</v>
+        <v>3540</v>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BB_Right Middle Finger_L1047_S2248__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3541__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Middle Finger</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -5990,37 +5990,37 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>2248</v>
+        <v>3541</v>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BB_Right Middle Finger_L1047_S2249__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3542__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Middle Finger</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6029,37 +6029,37 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>2249</v>
+        <v>3542</v>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BB_Right Middle Finger_L1047_S2250__19_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3543__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>L1047</t>
+          <t>L1061</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Middle Finger</t>
+          <t>Hallux</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6068,18 +6068,18 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>2250</v>
+        <v>3543</v>
       </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" s="2" t="n">
-        <v>44335</v>
+        <v>44347</v>
       </c>
       <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3482__31_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3544__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>3482</v>
+        <v>3544</v>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" s="2" t="n">
@@ -6118,7 +6118,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3534__31_05_2021.dcm</t>
+          <t>CH_Right Hallux_L1061_S3545__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>3534</v>
+        <v>3545</v>
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" s="2" t="n">
@@ -6157,26 +6157,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3535__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3528__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>3535</v>
+        <v>3528</v>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" s="2" t="n">
@@ -6196,26 +6196,26 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3536__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3529__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>3536</v>
+        <v>3529</v>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" s="2" t="n">
@@ -6235,26 +6235,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3537__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3530__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>3537</v>
+        <v>3530</v>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" s="2" t="n">
@@ -6274,26 +6274,26 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3538__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3531__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>3538</v>
+        <v>3531</v>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" s="2" t="n">
@@ -6313,26 +6313,26 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3539__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3532__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3539</v>
+        <v>3532</v>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" s="2" t="n">
@@ -6352,26 +6352,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3540__31_05_2021.dcm</t>
+          <t>CH_Right Hand_L1060_S3533__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1060</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>3540</v>
+        <v>3533</v>
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" s="2" t="n">
@@ -6391,26 +6391,26 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3541__31_05_2021.dcm</t>
+          <t>CS_Right Hand_L1096_S3558__31_05_2021.dcm</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1096</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>3541</v>
+        <v>3558</v>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" s="2" t="n">
@@ -6430,26 +6430,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3542__31_05_2021.dcm</t>
+          <t>DR_Right Hand_L1063_S2825__25_05_2021.dcm</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1063</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6458,37 +6458,37 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>3542</v>
+        <v>2825</v>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" s="2" t="n">
-        <v>44347</v>
+        <v>44341</v>
       </c>
       <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CH_Right Hallux_L1061_S3543__31_05_2021.dcm</t>
+          <t>GM_Right Hand_L1040_S2068__18_05_2021.dcm</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>L1061</t>
+          <t>L1040</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Hallux</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6497,442 +6497,13 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>3543</v>
+        <v>2068</v>
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" s="2" t="n">
-        <v>44347</v>
+        <v>44334</v>
       </c>
       <c r="M155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>CH_Right Hallux_L1061_S3544__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>L1061</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Foot</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Hallux</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J156" t="n">
-        <v>3544</v>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>CH_Right Hallux_L1061_S3545__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>L1061</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Foot</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Hallux</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>3545</v>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3528__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J158" t="n">
-        <v>3528</v>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3529__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J159" t="n">
-        <v>3529</v>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3530__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
-        <v>3530</v>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3531__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J161" t="n">
-        <v>3531</v>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3532__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>3532</v>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CH_Right Hand_L1060_S3533__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>L1060</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>3533</v>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>CS_Right Hand_L1096_S3558__31_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>L1096</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J164" t="n">
-        <v>3558</v>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" s="2" t="n">
-        <v>44347</v>
-      </c>
-      <c r="M164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>DR_Right Hand_L1063_S2825__25_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>L1063</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>2825</v>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" s="2" t="n">
-        <v>44341</v>
-      </c>
-      <c r="M165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>GM_Right Hand_L1040_S2068__18_05_2021.dcm</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>L1040</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Hand</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="J166" t="n">
-        <v>2068</v>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" s="2" t="n">
-        <v>44334</v>
-      </c>
-      <c r="M166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
